--- a/exports/maintenance_report.xlsx
+++ b/exports/maintenance_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,6 +419,14 @@
   </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -433,12 +441,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Engineer Name</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Maintenance Date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -455,168 +463,168 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MNT006</t>
+          <t>MNT001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AST006</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Harsh Yadav</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46272</v>
+          <t>AST001</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Amit Sharma</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Printer Replace</t>
+          <t>Battery Replaced</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MNT005</t>
+          <t>MNT002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AST005</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Rohit Gupta</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46218</v>
+          <t>AST002</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rahul Kumar</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Display Cable Changed</t>
+          <t>RAM Upgraded</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MNT004</t>
+          <t>MNT003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AST004</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ankit Singh</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46215</v>
+          <t>AST003</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Suresh Verma</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Keyboard Replaced</t>
+          <t>Printer Roller Changed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MNT003</t>
+          <t>MNT004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AST003</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Suresh Verma</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46213</v>
+          <t>AST004</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ankit Singh</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Printer Roller Changed</t>
+          <t>Keyboard Replaced</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MNT002</t>
+          <t>MNT005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AST002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Rahul Kumar</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46211</v>
+          <t>AST005</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rohit Gupta</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RAM Upgraded</t>
+          <t>Display Cable Changed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MNT001</t>
+          <t>MNT006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AST001</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Amit Sharma</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46208</v>
+          <t>AST006</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Harsh Yadav</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Battery Replaced</t>
+          <t>Laptop is not working properly</t>
         </is>
       </c>
     </row>
